--- a/Tabelas/criterios_por_ano.xlsx
+++ b/Tabelas/criterios_por_ano.xlsx
@@ -824,49 +824,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>43.8</v>
+        <v>44.26</v>
       </c>
       <c r="D8" t="n">
-        <v>4.65</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>88.37</v>
+        <v>84.86</v>
       </c>
       <c r="G8" t="n">
-        <v>83.33</v>
+        <v>81.53</v>
       </c>
       <c r="H8" t="n">
-        <v>99.22</v>
+        <v>99.17</v>
       </c>
       <c r="I8" t="n">
-        <v>5.81</v>
+        <v>5.99</v>
       </c>
       <c r="J8" t="n">
-        <v>56.59</v>
+        <v>50.25</v>
       </c>
       <c r="K8" t="n">
-        <v>42.25</v>
+        <v>45.76</v>
       </c>
       <c r="L8" t="n">
-        <v>13.18</v>
+        <v>15.97</v>
       </c>
       <c r="M8" t="n">
-        <v>67.83</v>
+        <v>68.55</v>
       </c>
       <c r="N8" t="n">
-        <v>53.1</v>
+        <v>56.41</v>
       </c>
       <c r="O8" t="n">
-        <v>16.28</v>
+        <v>20.8</v>
       </c>
       <c r="P8" t="n">
-        <v>97.29000000000001</v>
+        <v>98.34</v>
       </c>
     </row>
   </sheetData>
